--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_12-08-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_12-08-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF645496-D596-4F7D-BBD5-856E3B1C6CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4893B37C-CCD9-442E-A872-03163713BAC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33165" yWindow="975" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33075" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -145,9 +145,6 @@
     <t>£21.10</t>
   </si>
   <si>
-    <t>£19.27</t>
-  </si>
-  <si>
     <t>£18.31</t>
   </si>
   <si>
@@ -178,9 +175,6 @@
     <t>£25.04</t>
   </si>
   <si>
-    <t>£20.83</t>
-  </si>
-  <si>
     <t>£22.39</t>
   </si>
   <si>
@@ -211,9 +205,6 @@
     <t>£26.34</t>
   </si>
   <si>
-    <t>£24.26</t>
-  </si>
-  <si>
     <t>£23.42</t>
   </si>
   <si>
@@ -250,9 +241,6 @@
     <t>£31.92</t>
   </si>
   <si>
-    <t>£27.59</t>
-  </si>
-  <si>
     <t>£28.86</t>
   </si>
   <si>
@@ -283,9 +271,6 @@
     <t>£33.06</t>
   </si>
   <si>
-    <t>£31.06</t>
-  </si>
-  <si>
     <t>£32.48</t>
   </si>
   <si>
@@ -343,9 +328,6 @@
     <t>£40.31</t>
   </si>
   <si>
-    <t>£40.83</t>
-  </si>
-  <si>
     <t>£37.29</t>
   </si>
   <si>
@@ -367,9 +349,6 @@
     <t>£39.85</t>
   </si>
   <si>
-    <t>£43.06</t>
-  </si>
-  <si>
     <t>£38.84</t>
   </si>
   <si>
@@ -418,9 +397,6 @@
     <t>£102.12</t>
   </si>
   <si>
-    <t>£55.70</t>
-  </si>
-  <si>
     <t>REC120mm</t>
   </si>
   <si>
@@ -478,9 +454,6 @@
     <t>£63.05</t>
   </si>
   <si>
-    <t>£74.88</t>
-  </si>
-  <si>
     <t>£56.17</t>
   </si>
   <si>
@@ -505,9 +478,6 @@
     <t>£65.55</t>
   </si>
   <si>
-    <t>£66.58</t>
-  </si>
-  <si>
     <t>£60.64</t>
   </si>
   <si>
@@ -541,9 +511,6 @@
     <t>£66.70</t>
   </si>
   <si>
-    <t>£78.08</t>
-  </si>
-  <si>
     <t>£57.57</t>
   </si>
   <si>
@@ -649,9 +616,6 @@
     <t>£836.5</t>
   </si>
   <si>
-    <t>£463.00</t>
-  </si>
-  <si>
     <t>£594.55</t>
   </si>
   <si>
@@ -694,9 +658,6 @@
     <t>£678.81</t>
   </si>
   <si>
-    <t>£370.40</t>
-  </si>
-  <si>
     <t>£795.39</t>
   </si>
   <si>
@@ -806,6 +767,45 @@
   </si>
   <si>
     <t>£716.05</t>
+  </si>
+  <si>
+    <t>£25.00</t>
+  </si>
+  <si>
+    <t>£29.11</t>
+  </si>
+  <si>
+    <t>£33.11</t>
+  </si>
+  <si>
+    <t>£37.27</t>
+  </si>
+  <si>
+    <t>£48.99</t>
+  </si>
+  <si>
+    <t>£51.67</t>
+  </si>
+  <si>
+    <t>£66.84</t>
+  </si>
+  <si>
+    <t>£79.89</t>
+  </si>
+  <si>
+    <t>£89.86</t>
+  </si>
+  <si>
+    <t>£93.69</t>
+  </si>
+  <si>
+    <t>£99.37</t>
+  </si>
+  <si>
+    <t>£657.00</t>
+  </si>
+  <si>
+    <t>£711.4</t>
   </si>
 </sst>
 </file>
@@ -1244,7 +1244,7 @@
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="G2" t="s">
         <v>21</v>
@@ -1271,7 +1271,7 @@
         <v>28</v>
       </c>
       <c r="O2" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="P2" t="s">
         <v>29</v>
@@ -1300,7 +1300,7 @@
         <v>34</v>
       </c>
       <c r="F3" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="G3" t="s">
         <v>35</v>
@@ -1324,390 +1324,390 @@
         <v>40</v>
       </c>
       <c r="N3" t="s">
-        <v>41</v>
+        <v>249</v>
       </c>
       <c r="O3" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="P3" t="s">
         <v>29</v>
       </c>
       <c r="Q3" t="s">
+        <v>41</v>
+      </c>
+      <c r="R3" t="s">
         <v>42</v>
-      </c>
-      <c r="R3" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" t="s">
         <v>44</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>45</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>215</v>
+      </c>
+      <c r="G4" t="s">
         <v>46</v>
       </c>
-      <c r="D4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J4" t="s">
         <v>228</v>
       </c>
-      <c r="G4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>49</v>
       </c>
-      <c r="J4" t="s">
-        <v>241</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" t="s">
         <v>50</v>
       </c>
-      <c r="L4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
+        <v>250</v>
+      </c>
+      <c r="O4" t="s">
         <v>51</v>
-      </c>
-      <c r="N4" t="s">
-        <v>52</v>
-      </c>
-      <c r="O4" t="s">
-        <v>53</v>
       </c>
       <c r="P4" t="s">
         <v>29</v>
       </c>
       <c r="Q4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" t="s">
         <v>55</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" t="s">
+        <v>216</v>
+      </c>
+      <c r="G5" t="s">
         <v>56</v>
       </c>
-      <c r="C5" t="s">
+      <c r="H5" t="s">
         <v>57</v>
       </c>
-      <c r="D5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="I5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J5" t="s">
         <v>229</v>
       </c>
-      <c r="G5" t="s">
-        <v>58</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="K5" t="s">
         <v>59</v>
       </c>
-      <c r="I5" t="s">
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" t="s">
         <v>60</v>
       </c>
-      <c r="J5" t="s">
-        <v>242</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="N5" t="s">
+        <v>251</v>
+      </c>
+      <c r="O5" t="s">
         <v>61</v>
-      </c>
-      <c r="L5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" t="s">
-        <v>62</v>
-      </c>
-      <c r="N5" t="s">
-        <v>63</v>
-      </c>
-      <c r="O5" t="s">
-        <v>64</v>
       </c>
       <c r="P5" t="s">
         <v>29</v>
       </c>
       <c r="Q5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="R5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" t="s">
+        <v>217</v>
+      </c>
+      <c r="G6" t="s">
         <v>67</v>
       </c>
-      <c r="B6" t="s">
+      <c r="H6" t="s">
         <v>68</v>
       </c>
-      <c r="C6" t="s">
+      <c r="I6" t="s">
         <v>69</v>
       </c>
-      <c r="D6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" t="s">
-        <v>69</v>
-      </c>
-      <c r="F6" t="s">
-        <v>230</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="J6" t="s">
         <v>70</v>
       </c>
-      <c r="H6" t="s">
+      <c r="K6" t="s">
         <v>71</v>
       </c>
-      <c r="I6" t="s">
+      <c r="L6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" t="s">
         <v>72</v>
       </c>
-      <c r="J6" t="s">
-        <v>73</v>
-      </c>
-      <c r="K6" t="s">
-        <v>74</v>
-      </c>
-      <c r="L6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M6" t="s">
-        <v>75</v>
-      </c>
       <c r="N6" t="s">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="O6" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="P6" t="s">
         <v>29</v>
       </c>
       <c r="Q6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="R6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" t="s">
+        <v>218</v>
+      </c>
+      <c r="G7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7" t="s">
         <v>78</v>
       </c>
-      <c r="B7" t="s">
+      <c r="I7" t="s">
         <v>79</v>
       </c>
-      <c r="C7" t="s">
+      <c r="J7" t="s">
         <v>80</v>
       </c>
-      <c r="D7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F7" t="s">
-        <v>231</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="K7" t="s">
         <v>81</v>
       </c>
-      <c r="H7" t="s">
+      <c r="L7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" t="s">
         <v>82</v>
       </c>
-      <c r="I7" t="s">
-        <v>83</v>
-      </c>
-      <c r="J7" t="s">
-        <v>84</v>
-      </c>
-      <c r="K7" t="s">
-        <v>85</v>
-      </c>
-      <c r="L7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7" t="s">
-        <v>86</v>
-      </c>
       <c r="N7" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="O7" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="P7" t="s">
         <v>29</v>
       </c>
       <c r="Q7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R7" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" t="s">
+        <v>86</v>
+      </c>
+      <c r="E8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F8" t="s">
+        <v>219</v>
+      </c>
+      <c r="G8" t="s">
+        <v>87</v>
+      </c>
+      <c r="H8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J8" t="s">
+        <v>230</v>
+      </c>
+      <c r="K8" t="s">
         <v>89</v>
       </c>
-      <c r="B8" t="s">
+      <c r="L8" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" t="s">
         <v>90</v>
       </c>
-      <c r="C8" t="s">
+      <c r="N8" t="s">
+        <v>253</v>
+      </c>
+      <c r="O8" t="s">
         <v>91</v>
-      </c>
-      <c r="D8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E8" t="s">
-        <v>91</v>
-      </c>
-      <c r="F8" t="s">
-        <v>232</v>
-      </c>
-      <c r="G8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I8" t="s">
-        <v>93</v>
-      </c>
-      <c r="J8" t="s">
-        <v>243</v>
-      </c>
-      <c r="K8" t="s">
-        <v>94</v>
-      </c>
-      <c r="L8" t="s">
-        <v>26</v>
-      </c>
-      <c r="M8" t="s">
-        <v>95</v>
-      </c>
-      <c r="N8" t="s">
-        <v>87</v>
-      </c>
-      <c r="O8" t="s">
-        <v>96</v>
       </c>
       <c r="P8" t="s">
         <v>29</v>
       </c>
       <c r="Q8" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="R8" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F9" t="s">
+        <v>220</v>
+      </c>
+      <c r="G9" t="s">
+        <v>96</v>
+      </c>
+      <c r="H9" t="s">
+        <v>97</v>
+      </c>
+      <c r="I9" t="s">
         <v>98</v>
       </c>
-      <c r="B9" t="s">
+      <c r="J9" t="s">
         <v>99</v>
       </c>
-      <c r="C9" t="s">
+      <c r="K9" t="s">
         <v>100</v>
       </c>
-      <c r="D9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F9" t="s">
-        <v>233</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="L9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" t="s">
         <v>101</v>
       </c>
-      <c r="H9" t="s">
-        <v>102</v>
-      </c>
-      <c r="I9" t="s">
-        <v>103</v>
-      </c>
-      <c r="J9" t="s">
-        <v>104</v>
-      </c>
-      <c r="K9" t="s">
-        <v>105</v>
-      </c>
-      <c r="L9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M9" t="s">
-        <v>106</v>
-      </c>
       <c r="N9" t="s">
-        <v>107</v>
+        <v>254</v>
       </c>
       <c r="O9" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="P9" t="s">
         <v>29</v>
       </c>
       <c r="Q9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="R9" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B10" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C10" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E10" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F10" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="G10" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="H10" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="I10" t="s">
         <v>29</v>
       </c>
       <c r="J10" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="K10" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="L10" t="s">
         <v>26</v>
@@ -1716,98 +1716,98 @@
         <v>26</v>
       </c>
       <c r="N10" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="O10" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="P10" t="s">
         <v>29</v>
       </c>
       <c r="Q10" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="R10" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" t="s">
+        <v>106</v>
+      </c>
+      <c r="F11" t="s">
+        <v>222</v>
+      </c>
+      <c r="G11" t="s">
         <v>112</v>
       </c>
-      <c r="D11" t="s">
-        <v>112</v>
-      </c>
-      <c r="E11" t="s">
-        <v>112</v>
-      </c>
-      <c r="F11" t="s">
-        <v>235</v>
-      </c>
-      <c r="G11" t="s">
-        <v>119</v>
-      </c>
       <c r="H11" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="I11" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="J11" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="K11" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="L11" t="s">
         <v>26</v>
       </c>
       <c r="M11" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="N11" t="s">
-        <v>115</v>
+        <v>255</v>
       </c>
       <c r="O11" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="P11" t="s">
         <v>29</v>
       </c>
       <c r="Q11" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="R11" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="B12" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C12" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D12" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E12" t="s">
         <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="G12" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="H12" t="s">
         <v>26</v>
@@ -1816,7 +1816,7 @@
         <v>29</v>
       </c>
       <c r="J12" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="K12" t="s">
         <v>26</v>
@@ -1825,19 +1825,19 @@
         <v>26</v>
       </c>
       <c r="M12" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="N12" t="s">
-        <v>132</v>
+        <v>29</v>
       </c>
       <c r="O12" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="P12" t="s">
         <v>29</v>
       </c>
       <c r="Q12" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="R12" t="s">
         <v>26</v>
@@ -1845,111 +1845,111 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>125</v>
+      </c>
+      <c r="B13" t="s">
+        <v>126</v>
+      </c>
+      <c r="C13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D13" t="s">
+        <v>127</v>
+      </c>
+      <c r="E13" t="s">
+        <v>127</v>
+      </c>
+      <c r="F13" t="s">
+        <v>224</v>
+      </c>
+      <c r="G13" t="s">
+        <v>128</v>
+      </c>
+      <c r="H13" t="s">
+        <v>129</v>
+      </c>
+      <c r="I13" t="s">
+        <v>130</v>
+      </c>
+      <c r="J13" t="s">
+        <v>131</v>
+      </c>
+      <c r="K13" t="s">
+        <v>132</v>
+      </c>
+      <c r="L13" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" t="s">
         <v>133</v>
       </c>
-      <c r="B13" t="s">
-        <v>134</v>
-      </c>
-      <c r="C13" t="s">
-        <v>135</v>
-      </c>
-      <c r="D13" t="s">
-        <v>135</v>
-      </c>
-      <c r="E13" t="s">
-        <v>135</v>
-      </c>
-      <c r="F13" t="s">
-        <v>237</v>
-      </c>
-      <c r="G13" t="s">
-        <v>136</v>
-      </c>
-      <c r="H13" t="s">
-        <v>137</v>
-      </c>
-      <c r="I13" t="s">
-        <v>138</v>
-      </c>
-      <c r="J13" t="s">
-        <v>139</v>
-      </c>
-      <c r="K13" t="s">
-        <v>140</v>
-      </c>
-      <c r="L13" t="s">
-        <v>26</v>
-      </c>
-      <c r="M13" t="s">
-        <v>141</v>
-      </c>
       <c r="N13" t="s">
-        <v>132</v>
+        <v>256</v>
       </c>
       <c r="O13" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="P13" t="s">
         <v>29</v>
       </c>
       <c r="Q13" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="R13" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>135</v>
+      </c>
+      <c r="B14" t="s">
+        <v>136</v>
+      </c>
+      <c r="C14" t="s">
+        <v>137</v>
+      </c>
+      <c r="D14" t="s">
+        <v>137</v>
+      </c>
+      <c r="E14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" t="s">
+        <v>225</v>
+      </c>
+      <c r="G14" t="s">
+        <v>138</v>
+      </c>
+      <c r="H14" t="s">
+        <v>139</v>
+      </c>
+      <c r="I14" t="s">
+        <v>140</v>
+      </c>
+      <c r="J14" t="s">
+        <v>141</v>
+      </c>
+      <c r="K14" t="s">
+        <v>142</v>
+      </c>
+      <c r="L14" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" t="s">
         <v>143</v>
       </c>
-      <c r="B14" t="s">
-        <v>144</v>
-      </c>
-      <c r="C14" t="s">
-        <v>145</v>
-      </c>
-      <c r="D14" t="s">
-        <v>145</v>
-      </c>
-      <c r="E14" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" t="s">
-        <v>238</v>
-      </c>
-      <c r="G14" t="s">
-        <v>146</v>
-      </c>
-      <c r="H14" t="s">
-        <v>147</v>
-      </c>
-      <c r="I14" t="s">
-        <v>148</v>
-      </c>
-      <c r="J14" t="s">
-        <v>149</v>
-      </c>
-      <c r="K14" t="s">
-        <v>150</v>
-      </c>
-      <c r="L14" t="s">
-        <v>26</v>
-      </c>
-      <c r="M14" t="s">
-        <v>151</v>
-      </c>
       <c r="N14" t="s">
-        <v>152</v>
+        <v>257</v>
       </c>
       <c r="O14" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="P14" t="s">
         <v>29</v>
       </c>
       <c r="Q14" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="R14" t="s">
         <v>26</v>
@@ -1957,55 +1957,55 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="B15" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="C15" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D15" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E15" t="s">
         <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="G15" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="H15" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="I15" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="J15" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="K15" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="L15" t="s">
         <v>26</v>
       </c>
       <c r="M15" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="N15" t="s">
-        <v>161</v>
+        <v>258</v>
       </c>
       <c r="O15" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="P15" t="s">
         <v>29</v>
       </c>
       <c r="Q15" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="R15" t="s">
         <v>26</v>
@@ -2013,72 +2013,72 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B16" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C16" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="D16" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E16" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="F16" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="G16" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="H16" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="I16" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="J16" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="K16" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="L16" t="s">
         <v>26</v>
       </c>
       <c r="M16" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="N16" t="s">
-        <v>173</v>
+        <v>259</v>
       </c>
       <c r="O16" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="P16" t="s">
         <v>29</v>
       </c>
       <c r="Q16" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="R16" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="B17" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="C17" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="D17" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="E17" t="s">
         <v>26</v>
@@ -2125,16 +2125,16 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="B18" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="C18" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="D18" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E18" t="s">
         <v>26</v>
@@ -2143,7 +2143,7 @@
         <v>26</v>
       </c>
       <c r="G18" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="H18" t="s">
         <v>26</v>
@@ -2152,7 +2152,7 @@
         <v>26</v>
       </c>
       <c r="J18" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="K18" t="s">
         <v>26</v>
@@ -2164,10 +2164,10 @@
         <v>26</v>
       </c>
       <c r="N18" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="O18" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="P18" t="s">
         <v>29</v>
@@ -2181,16 +2181,16 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="B19" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="C19" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="D19" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="E19" t="s">
         <v>26</v>
@@ -2199,7 +2199,7 @@
         <v>26</v>
       </c>
       <c r="G19" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="H19" t="s">
         <v>26</v>
@@ -2208,7 +2208,7 @@
         <v>26</v>
       </c>
       <c r="J19" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="K19" t="s">
         <v>26</v>
@@ -2220,10 +2220,10 @@
         <v>26</v>
       </c>
       <c r="N19" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="O19" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="P19" t="s">
         <v>29</v>
@@ -2232,21 +2232,21 @@
         <v>26</v>
       </c>
       <c r="R19" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="B20" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="C20" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="D20" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="E20" t="s">
         <v>26</v>
@@ -2264,7 +2264,7 @@
         <v>26</v>
       </c>
       <c r="J20" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="K20" t="s">
         <v>26</v>
@@ -2293,16 +2293,16 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="B21" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="C21" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="D21" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="E21" t="s">
         <v>26</v>
@@ -2320,7 +2320,7 @@
         <v>26</v>
       </c>
       <c r="J21" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="K21" t="s">
         <v>26</v>
@@ -2349,16 +2349,16 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="B22" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="C22" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="D22" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="E22" t="s">
         <v>26</v>
@@ -2376,7 +2376,7 @@
         <v>26</v>
       </c>
       <c r="J22" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="K22" t="s">
         <v>26</v>
@@ -2405,28 +2405,28 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="B23" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="C23" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="D23" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="E23" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="F23" t="s">
         <v>26</v>
       </c>
       <c r="G23" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="H23" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="I23" t="s">
         <v>26</v>
@@ -2435,19 +2435,19 @@
         <v>26</v>
       </c>
       <c r="K23" t="s">
+        <v>247</v>
+      </c>
+      <c r="L23" t="s">
+        <v>26</v>
+      </c>
+      <c r="M23" t="s">
+        <v>197</v>
+      </c>
+      <c r="N23" t="s">
         <v>260</v>
       </c>
-      <c r="L23" t="s">
-        <v>26</v>
-      </c>
-      <c r="M23" t="s">
-        <v>208</v>
-      </c>
-      <c r="N23" t="s">
-        <v>209</v>
-      </c>
       <c r="O23" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="P23" t="s">
         <v>26</v>
@@ -2456,33 +2456,33 @@
         <v>26</v>
       </c>
       <c r="R23" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="B24" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C24" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="D24" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="E24" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="F24" t="s">
         <v>26</v>
       </c>
       <c r="G24" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="H24" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="I24" t="s">
         <v>26</v>
@@ -2491,7 +2491,7 @@
         <v>26</v>
       </c>
       <c r="K24" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="L24" t="s">
         <v>26</v>
@@ -2500,10 +2500,10 @@
         <v>29</v>
       </c>
       <c r="N24" t="s">
-        <v>209</v>
+        <v>260</v>
       </c>
       <c r="O24" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="P24" t="s">
         <v>26</v>
@@ -2512,33 +2512,33 @@
         <v>26</v>
       </c>
       <c r="R24" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="B25" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="C25" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="D25" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="E25" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="F25" t="s">
         <v>26</v>
       </c>
       <c r="G25" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="H25" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="I25" t="s">
         <v>26</v>
@@ -2547,7 +2547,7 @@
         <v>26</v>
       </c>
       <c r="K25" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="L25" t="s">
         <v>26</v>
@@ -2556,10 +2556,10 @@
         <v>29</v>
       </c>
       <c r="N25" t="s">
-        <v>224</v>
+        <v>261</v>
       </c>
       <c r="O25" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="P25" t="s">
         <v>26</v>
@@ -2568,7 +2568,7 @@
         <v>26</v>
       </c>
       <c r="R25" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
